--- a/exports/trend_1d/GVT&D_full_report.xlsx
+++ b/exports/trend_1d/GVT&D_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.94</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42124</v>
+        <v>42128</v>
       </c>
       <c r="H2" t="n">
-        <v>519.25</v>
+        <v>506.7</v>
       </c>
       <c r="I2" t="n">
         <v>514.4094750350334</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K2" t="n">
-        <v>6.84</v>
+        <v>4.26</v>
       </c>
       <c r="L2" t="n">
         <v>3.29</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>17.65</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42192</v>
+        <v>42193</v>
       </c>
       <c r="H3" t="n">
-        <v>555.79</v>
+        <v>584.95</v>
       </c>
       <c r="I3" t="n">
         <v>560.7193598227357</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.69</v>
+        <v>-15.44</v>
       </c>
       <c r="L3" t="n">
-        <v>12.29</v>
+        <v>16.83</v>
       </c>
       <c r="M3" t="n">
         <v>2.58</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>13.46</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H4" t="n">
-        <v>565.45</v>
+        <v>538.54</v>
       </c>
       <c r="I4" t="n">
         <v>541.2950080255952</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.33</v>
+        <v>-7.93</v>
       </c>
       <c r="L4" t="n">
-        <v>6.49</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>3.23</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>4.76</v>
       </c>
       <c r="O4" t="n">
         <v>5.25</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.29</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42444</v>
+        <v>42445</v>
       </c>
       <c r="H5" t="n">
-        <v>398.3</v>
+        <v>408.1</v>
       </c>
       <c r="I5" t="n">
         <v>407.3750391026261</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K5" t="n">
-        <v>26.04</v>
+        <v>24.22</v>
       </c>
       <c r="L5" t="n">
         <v>10.3</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>14.54</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42493</v>
+        <v>42494</v>
       </c>
       <c r="H6" t="n">
-        <v>378.55</v>
+        <v>354.1</v>
       </c>
       <c r="I6" t="n">
         <v>372.5195719920053</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.24</v>
+        <v>-13.23</v>
       </c>
       <c r="L6" t="n">
-        <v>9.56</v>
+        <v>13.97</v>
       </c>
       <c r="M6" t="n">
-        <v>1.24</v>
+        <v>4.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>6.46</v>
       </c>
       <c r="O6" t="n">
         <v>2.46</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>15.27</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42527</v>
+        <v>42528</v>
       </c>
       <c r="H7" t="n">
-        <v>360.2</v>
+        <v>368.1</v>
       </c>
       <c r="I7" t="n">
         <v>363.1487889200509</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.72</v>
+        <v>-3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>4.46</v>
+        <v>4.74</v>
       </c>
       <c r="M7" t="n">
         <v>1.5</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.99</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42591</v>
+        <v>42592</v>
       </c>
       <c r="H8" t="n">
-        <v>340</v>
+        <v>333.85</v>
       </c>
       <c r="I8" t="n">
         <v>335.9344289424503</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.63</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>10.35</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.9</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42629</v>
+        <v>42632</v>
       </c>
       <c r="H9" t="n">
-        <v>340</v>
+        <v>343.6</v>
       </c>
       <c r="I9" t="n">
         <v>340.9870927173232</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.84</v>
+        <v>-2.92</v>
       </c>
       <c r="L9" t="n">
         <v>4.84</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.63</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42698</v>
+        <v>42699</v>
       </c>
       <c r="H10" t="n">
-        <v>321.65</v>
+        <v>315.15</v>
       </c>
       <c r="I10" t="n">
         <v>316.6486925364028</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.39</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>12.69</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.54</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42746</v>
+        <v>42747</v>
       </c>
       <c r="H11" t="n">
-        <v>307</v>
+        <v>314.8</v>
       </c>
       <c r="I11" t="n">
         <v>313.723233840941</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" t="n">
-        <v>2.59</v>
+        <v>0.11</v>
       </c>
       <c r="L11" t="n">
         <v>7.09</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>11.1</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42797</v>
+        <v>42800</v>
       </c>
       <c r="H12" t="n">
-        <v>293.8</v>
+        <v>285.7</v>
       </c>
       <c r="I12" t="n">
         <v>289.2959556895607</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.67</v>
+        <v>-9.24</v>
       </c>
       <c r="L12" t="n">
-        <v>7.24</v>
+        <v>9.75</v>
       </c>
       <c r="M12" t="n">
         <v>0.45</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42809</v>
+        <v>42810</v>
       </c>
       <c r="H13" t="n">
-        <v>301.35</v>
+        <v>307.2</v>
       </c>
       <c r="I13" t="n">
         <v>306.3488517708749</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.48</v>
+        <v>-7.53</v>
       </c>
       <c r="L13" t="n">
-        <v>6.3</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>2.06</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.49</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42892</v>
+        <v>42893</v>
       </c>
       <c r="H14" t="n">
-        <v>339.75</v>
+        <v>336.5</v>
       </c>
       <c r="I14" t="n">
         <v>337.1006752865142</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K14" t="n">
-        <v>10.6</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>2.33</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>11.88</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42941</v>
+        <v>42942</v>
       </c>
       <c r="H15" t="n">
-        <v>329</v>
+        <v>394</v>
       </c>
       <c r="I15" t="n">
         <v>344.1965857945097</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K15" t="n">
-        <v>2.23</v>
+        <v>-17.09</v>
       </c>
       <c r="L15" t="n">
-        <v>3.71</v>
+        <v>17.33</v>
       </c>
       <c r="M15" t="n">
-        <v>1.31</v>
+        <v>7.29</v>
       </c>
       <c r="N15" t="n">
-        <v>3.08</v>
+        <v>19.76</v>
       </c>
       <c r="O15" t="n">
         <v>-0.96</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>16.15</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H16" t="n">
-        <v>423.75</v>
+        <v>400.8</v>
       </c>
       <c r="I16" t="n">
         <v>408.9092660862194</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K16" t="n">
-        <v>7.55</v>
+        <v>1.73</v>
       </c>
       <c r="L16" t="n">
         <v>11.68</v>
@@ -1353,7 +1544,7 @@
         <v>3.94</v>
       </c>
       <c r="N16" t="n">
-        <v>3.96</v>
+        <v>5.42</v>
       </c>
       <c r="O16" t="n">
         <v>19.76</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>16.89</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43446</v>
+        <v>43447</v>
       </c>
       <c r="H17" t="n">
-        <v>247.35</v>
+        <v>260.95</v>
       </c>
       <c r="I17" t="n">
         <v>251.5436452842839</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K17" t="n">
-        <v>38.29</v>
+        <v>34.89</v>
       </c>
       <c r="L17" t="n">
         <v>7.67</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>210</v>
+        <v>211</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>11</v>
+      </c>
+      <c r="U17" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>14.05</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H18" t="n">
-        <v>288.05</v>
+        <v>286.35</v>
       </c>
       <c r="I18" t="n">
         <v>286.3765851957062</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K18" t="n">
-        <v>10.39</v>
+        <v>9.73</v>
       </c>
       <c r="L18" t="n">
         <v>4.92</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>14.33</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H19" t="n">
-        <v>231.25</v>
+        <v>272.85</v>
       </c>
       <c r="I19" t="n">
         <v>255.2233773942985</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K19" t="n">
-        <v>19.24</v>
+        <v>4.71</v>
       </c>
       <c r="L19" t="n">
         <v>11.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.3</v>
+        <v>3.29</v>
       </c>
       <c r="N19" t="n">
-        <v>5.94</v>
+        <v>17.99</v>
       </c>
       <c r="O19" t="n">
         <v>-0.59</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>20.83</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H20" t="n">
-        <v>241.95</v>
+        <v>232.05</v>
       </c>
       <c r="I20" t="n">
         <v>237.3369423610191</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" t="n">
-        <v>-11.32</v>
+        <v>-14.95</v>
       </c>
       <c r="L20" t="n">
-        <v>14.15</v>
+        <v>15.34</v>
       </c>
       <c r="M20" t="n">
         <v>3.98</v>
       </c>
       <c r="N20" t="n">
-        <v>3.41</v>
+        <v>4.09</v>
       </c>
       <c r="O20" t="n">
         <v>17.99</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>15.85</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H21" t="n">
-        <v>155.5</v>
+        <v>180.2</v>
       </c>
       <c r="I21" t="n">
         <v>171.5623126377974</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K21" t="n">
-        <v>32.99</v>
+        <v>22.34</v>
       </c>
       <c r="L21" t="n">
         <v>6.44</v>
@@ -1638,7 +1889,7 @@
         <v>2.38</v>
       </c>
       <c r="N21" t="n">
-        <v>7</v>
+        <v>15.88</v>
       </c>
       <c r="O21" t="n">
         <v>-4.09</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>22.84</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43774</v>
+        <v>43775</v>
       </c>
       <c r="H22" t="n">
-        <v>193.5</v>
+        <v>170.7</v>
       </c>
       <c r="I22" t="n">
         <v>172.0737783735606</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K22" t="n">
-        <v>7.38</v>
+        <v>-5.27</v>
       </c>
       <c r="L22" t="n">
         <v>12.68</v>
       </c>
       <c r="M22" t="n">
-        <v>2.12</v>
+        <v>3.88</v>
       </c>
       <c r="N22" t="n">
-        <v>5.22</v>
+        <v>11.78</v>
       </c>
       <c r="O22" t="n">
         <v>15.88</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>26.59</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H23" t="n">
-        <v>164.8</v>
+        <v>174.45</v>
       </c>
       <c r="I23" t="n">
         <v>165.3427595421913</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K23" t="n">
-        <v>3.46</v>
+        <v>-2.2</v>
       </c>
       <c r="L23" t="n">
         <v>11.28</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>16.56</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43874</v>
+        <v>43875</v>
       </c>
       <c r="H24" t="n">
-        <v>148.65</v>
+        <v>144.4</v>
       </c>
       <c r="I24" t="n">
         <v>146.2682297221284</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>-14.79</v>
+        <v>-17.23</v>
       </c>
       <c r="L24" t="n">
-        <v>15.88</v>
+        <v>17.57</v>
       </c>
       <c r="M24" t="n">
         <v>5.15</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>20.61</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43937</v>
+        <v>43938</v>
       </c>
       <c r="H25" t="n">
-        <v>88.84999999999999</v>
+        <v>93.25</v>
       </c>
       <c r="I25" t="n">
         <v>90.90610220504516</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K25" t="n">
-        <v>38.47</v>
+        <v>35.42</v>
       </c>
       <c r="L25" t="n">
         <v>3.74</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>24.57</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43956</v>
+        <v>43957</v>
       </c>
       <c r="H26" t="n">
-        <v>77.84999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>75.37688595281935</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>-16.51</v>
+        <v>-20.27</v>
       </c>
       <c r="L26" t="n">
-        <v>16.89</v>
+        <v>20.64</v>
       </c>
       <c r="M26" t="n">
         <v>4.16</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>24.35</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H27" t="n">
-        <v>72.05</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>73.15614303241307</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>3.09</v>
+        <v>-1.75</v>
       </c>
       <c r="L27" t="n">
         <v>6.79</v>
@@ -1980,7 +2303,7 @@
         <v>4.99</v>
       </c>
       <c r="N27" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
         <v>-4.5</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>17.23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H28" t="n">
-        <v>100.2</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>99.69703264777186</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K28" t="n">
-        <v>32.45</v>
+        <v>27.76</v>
       </c>
       <c r="L28" t="n">
         <v>11.43</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>18.15</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H29" t="n">
-        <v>91.90000000000001</v>
+        <v>93.45</v>
       </c>
       <c r="I29" t="n">
         <v>93.20089508030027</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K29" t="n">
-        <v>4.91</v>
+        <v>3.31</v>
       </c>
       <c r="L29" t="n">
         <v>9.73</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.47</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="H30" t="n">
-        <v>114.75</v>
+        <v>110.5</v>
       </c>
       <c r="I30" t="n">
         <v>113.1960474033102</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K30" t="n">
-        <v>22.79</v>
+        <v>18.25</v>
       </c>
       <c r="L30" t="n">
         <v>1.44</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>21.31</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44244</v>
+        <v>44245</v>
       </c>
       <c r="H31" t="n">
-        <v>122.95</v>
+        <v>131.75</v>
       </c>
       <c r="I31" t="n">
         <v>130.9418559161163</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
-        <v>-11.27</v>
+        <v>-19.23</v>
       </c>
       <c r="L31" t="n">
-        <v>14.84</v>
+        <v>20.27</v>
       </c>
       <c r="M31" t="n">
         <v>8.6</v>
       </c>
       <c r="N31" t="n">
-        <v>6.46</v>
+        <v>7.16</v>
       </c>
       <c r="O31" t="n">
         <v>-3.7</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>17.01</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H32" t="n">
-        <v>123.75</v>
+        <v>118.6</v>
       </c>
       <c r="I32" t="n">
         <v>118.9430313691867</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.07</v>
+        <v>-9.98</v>
       </c>
       <c r="L32" t="n">
-        <v>6.64</v>
+        <v>10.4</v>
       </c>
       <c r="M32" t="n">
         <v>0.88</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>22.98</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H33" t="n">
-        <v>121.7</v>
+        <v>131.2</v>
       </c>
       <c r="I33" t="n">
         <v>123.8839588307563</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.61</v>
+        <v>-10.62</v>
       </c>
       <c r="L33" t="n">
-        <v>8.43</v>
+        <v>12.14</v>
       </c>
       <c r="M33" t="n">
         <v>2.61</v>
       </c>
       <c r="N33" t="n">
-        <v>4.56</v>
+        <v>7.81</v>
       </c>
       <c r="O33" t="n">
         <v>-4.16</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>16.24</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44463</v>
+        <v>44466</v>
       </c>
       <c r="H34" t="n">
-        <v>130.65</v>
+        <v>126.9</v>
       </c>
       <c r="I34" t="n">
         <v>127.2946504558236</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.42</v>
+        <v>-3.28</v>
       </c>
       <c r="L34" t="n">
         <v>8.92</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.13</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44559</v>
+        <v>44560</v>
       </c>
       <c r="H35" t="n">
-        <v>127.7</v>
+        <v>130.3</v>
       </c>
       <c r="I35" t="n">
         <v>128.3020028648903</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.63</v>
+        <v>-2.68</v>
       </c>
       <c r="L35" t="n">
         <v>7.17</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H36" t="n">
-        <v>124.4</v>
+        <v>121.6</v>
       </c>
       <c r="I36" t="n">
         <v>123.1140042604161</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.53</v>
+        <v>-6.68</v>
       </c>
       <c r="L36" t="n">
         <v>8.67</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.74</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H37" t="n">
-        <v>98.3</v>
+        <v>103.85</v>
       </c>
       <c r="I37" t="n">
         <v>101.2505824294745</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K37" t="n">
-        <v>19.16</v>
+        <v>14.6</v>
       </c>
       <c r="L37" t="n">
         <v>3.45</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>15.69</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H38" t="n">
-        <v>112.15</v>
+        <v>106.55</v>
       </c>
       <c r="I38" t="n">
         <v>108.2880810663179</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K38" t="n">
-        <v>7.99</v>
+        <v>2.6</v>
       </c>
       <c r="L38" t="n">
         <v>4.96</v>
@@ -2607,7 +3062,7 @@
         <v>3.01</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>4.99</v>
       </c>
       <c r="O38" t="n">
         <v>5.65</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>18.28</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44757</v>
+        <v>44760</v>
       </c>
       <c r="H39" t="n">
-        <v>104.85</v>
+        <v>108.35</v>
       </c>
       <c r="I39" t="n">
         <v>108.1778267257977</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>1.6</v>
+        <v>-1.69</v>
       </c>
       <c r="L39" t="n">
         <v>5.16</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.8</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H40" t="n">
-        <v>124.45</v>
+        <v>120.75</v>
       </c>
       <c r="I40" t="n">
         <v>121.142052970362</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K40" t="n">
-        <v>14.86</v>
+        <v>11.44</v>
       </c>
       <c r="L40" t="n">
         <v>4.01</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.44</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45007</v>
+        <v>45008</v>
       </c>
       <c r="H41" t="n">
-        <v>118.15</v>
+        <v>119.1</v>
       </c>
       <c r="I41" t="n">
         <v>118.6721418738062</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K41" t="n">
-        <v>2.15</v>
+        <v>1.37</v>
       </c>
       <c r="L41" t="n">
         <v>4.18</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.43</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45076</v>
+        <v>45077</v>
       </c>
       <c r="H42" t="n">
-        <v>185.65</v>
+        <v>178.15</v>
       </c>
       <c r="I42" t="n">
         <v>183.7397501013262</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K42" t="n">
-        <v>55.88</v>
+        <v>49.58</v>
       </c>
       <c r="L42" t="n">
         <v>5.21</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>25.4</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45084</v>
+        <v>45085</v>
       </c>
       <c r="H43" t="n">
-        <v>207.9</v>
+        <v>218.25</v>
       </c>
       <c r="I43" t="n">
         <v>217.5384162753733</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>-16.7</v>
+        <v>-22.51</v>
       </c>
       <c r="L43" t="n">
-        <v>16.7</v>
+        <v>22.51</v>
       </c>
       <c r="M43" t="n">
         <v>2.25</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>17.82</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H44" t="n">
-        <v>374.65</v>
+        <v>360.25</v>
       </c>
       <c r="I44" t="n">
         <v>372.4775291318634</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K44" t="n">
-        <v>71.66</v>
+        <v>65.06</v>
       </c>
       <c r="L44" t="n">
         <v>10.52</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>20.51</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="H45" t="n">
-        <v>425.85</v>
+        <v>429.2</v>
       </c>
       <c r="I45" t="n">
         <v>428.1219389492506</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K45" t="n">
-        <v>-18.21</v>
+        <v>-19.14</v>
       </c>
       <c r="L45" t="n">
-        <v>19.36</v>
+        <v>23.53</v>
       </c>
       <c r="M45" t="n">
         <v>2.82</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.35</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H46" t="n">
-        <v>1453.6</v>
+        <v>1438.05</v>
       </c>
       <c r="I46" t="n">
         <v>1451.972918066571</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K46" t="n">
-        <v>238.68</v>
+        <v>235.05</v>
       </c>
       <c r="L46" t="n">
         <v>3.45</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>8</v>
+      </c>
+      <c r="U46" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>17.78</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="H47" t="n">
-        <v>1664.3</v>
+        <v>1747.5</v>
       </c>
       <c r="I47" t="n">
         <v>1693.78615661087</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>-15.73</v>
+        <v>-21.52</v>
       </c>
       <c r="L47" t="n">
-        <v>15.73</v>
+        <v>21.52</v>
       </c>
       <c r="M47" t="n">
         <v>5</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>15</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H48" t="n">
-        <v>1628.95</v>
+        <v>1569.7</v>
       </c>
       <c r="I48" t="n">
         <v>1574.910363177644</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.78</v>
+        <v>-10.17</v>
       </c>
       <c r="L48" t="n">
-        <v>8.44</v>
+        <v>11.42</v>
       </c>
       <c r="M48" t="n">
         <v>5</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>19.32</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45575</v>
+        <v>45576</v>
       </c>
       <c r="H49" t="n">
-        <v>1770.05</v>
+        <v>1775.7</v>
       </c>
       <c r="I49" t="n">
         <v>1774.547781268608</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K49" t="n">
-        <v>-12.76</v>
+        <v>-13.12</v>
       </c>
       <c r="L49" t="n">
-        <v>15.17</v>
+        <v>16.25</v>
       </c>
       <c r="M49" t="n">
         <v>4.99</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>15.71</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45677</v>
+        <v>45678</v>
       </c>
       <c r="H50" t="n">
-        <v>1894.55</v>
+        <v>1824.5</v>
       </c>
       <c r="I50" t="n">
         <v>1880.866534781318</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K50" t="n">
-        <v>6.69</v>
+        <v>2.75</v>
       </c>
       <c r="L50" t="n">
         <v>9.82</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>15.86</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H51" t="n">
-        <v>1545.35</v>
+        <v>1622.05</v>
       </c>
       <c r="I51" t="n">
         <v>1561.017607938194</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K51" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="L51" t="n">
         <v>4.07</v>
@@ -3348,7 +3959,7 @@
         <v>2.57</v>
       </c>
       <c r="N51" t="n">
-        <v>4.42</v>
+        <v>4.96</v>
       </c>
       <c r="O51" t="n">
         <v>-3.7</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>17.37</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H52" t="n">
-        <v>1402.5</v>
+        <v>1295.55</v>
       </c>
       <c r="I52" t="n">
         <v>1375.131290813819</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K52" t="n">
-        <v>-13.54</v>
+        <v>-20.13</v>
       </c>
       <c r="L52" t="n">
-        <v>14.31</v>
+        <v>21.6</v>
       </c>
       <c r="M52" t="n">
-        <v>1.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>7.63</v>
       </c>
       <c r="O52" t="n">
         <v>4.96</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>20.97</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45772</v>
+        <v>45775</v>
       </c>
       <c r="H53" t="n">
-        <v>1479.4</v>
+        <v>1535.2</v>
       </c>
       <c r="I53" t="n">
         <v>1521.696552585001</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K53" t="n">
-        <v>-14.19</v>
+        <v>-18.5</v>
       </c>
       <c r="L53" t="n">
         <v>19.64</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>16.08</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H54" t="n">
-        <v>2959.6</v>
+        <v>2817.6</v>
       </c>
       <c r="I54" t="n">
         <v>2861.608562735027</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K54" t="n">
-        <v>92.78</v>
+        <v>83.53</v>
       </c>
       <c r="L54" t="n">
         <v>4.52</v>
@@ -3519,7 +4166,7 @@
         <v>3.62</v>
       </c>
       <c r="N54" t="n">
-        <v>4.39</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>3.77</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>14.11</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="H55" t="n">
-        <v>3097.8</v>
+        <v>3129.9</v>
       </c>
       <c r="I55" t="n">
         <v>3122.055905193824</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K55" t="n">
-        <v>-9.94</v>
+        <v>-11.08</v>
       </c>
       <c r="L55" t="n">
         <v>17.97</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>14</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="H56" t="n">
-        <v>2898.1</v>
+        <v>2718.2</v>
       </c>
       <c r="I56" t="n">
         <v>2788.615336026527</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>-7.41</v>
+        <v>-13.15</v>
       </c>
       <c r="L56" t="n">
-        <v>10.2</v>
+        <v>13.61</v>
       </c>
       <c r="M56" t="n">
         <v>1.84</v>
       </c>
       <c r="N56" t="n">
-        <v>4.69</v>
+        <v>6.21</v>
       </c>
       <c r="O56" t="n">
         <v>1.04</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>18.05</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H57" t="n">
-        <v>2905</v>
+        <v>3157.9</v>
       </c>
       <c r="I57" t="n">
         <v>2933.965228107415</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.87</v>
+        <v>-16.18</v>
       </c>
       <c r="L57" t="n">
-        <v>7.49</v>
+        <v>17.64</v>
       </c>
       <c r="M57" t="n">
-        <v>1.17</v>
+        <v>5.2</v>
       </c>
       <c r="N57" t="n">
-        <v>6.38</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O57" t="n">
         <v>-6.21</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>15.88</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="H58" t="n">
-        <v>4822.8</v>
+        <v>4401.5</v>
       </c>
       <c r="I58" t="n">
         <v>4765.454207743604</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K58" t="n">
-        <v>52.72</v>
+        <v>39.38</v>
       </c>
       <c r="L58" t="n">
         <v>5.43</v>
@@ -3747,7 +4442,7 @@
         <v>5.06</v>
       </c>
       <c r="N58" t="n">
-        <v>7.64</v>
+        <v>8.74</v>
       </c>
       <c r="O58" t="n">
         <v>8.710000000000001</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>19.94</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="H59" t="n">
-        <v>4367.2</v>
+        <v>4750</v>
       </c>
       <c r="I59" t="n">
         <v>4561.416164019858</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K59" t="n">
-        <v>0.78</v>
+        <v>-7.92</v>
       </c>
       <c r="L59" t="n">
-        <v>7.66</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>3.51</v>
+        <v>6.16</v>
       </c>
       <c r="N59" t="n">
-        <v>4.4</v>
+        <v>8.77</v>
       </c>
       <c r="O59" t="n">
         <v>-8.74</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>11.76</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H60" t="n">
-        <v>4280</v>
+        <v>4203</v>
       </c>
       <c r="I60" t="n">
         <v>4216.955934301755</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K60" t="n">
-        <v>-9.890000000000001</v>
+        <v>-11.52</v>
       </c>
       <c r="L60" t="n">
         <v>12.64</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>11.15</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="H61" t="n">
-        <v>3980</v>
+        <v>4075</v>
       </c>
       <c r="I61" t="n">
         <v>4059.535039383095</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>5.31</v>
+        <v>3.05</v>
       </c>
       <c r="L61" t="n">
         <v>3.26</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3978,6 +4721,12 @@
       <c r="Q62" t="n">
         <v>1</v>
       </c>
+      <c r="R62" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8936,7 +9685,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.09999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="6">
@@ -8946,7 +9695,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -8956,7 +9705,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8">
@@ -8966,7 +9715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -8976,7 +9725,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="10">
@@ -8986,7 +9735,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154.1</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="11">
@@ -8996,7 +9745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -9006,7 +9755,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -9016,7 +9765,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="14">
@@ -9026,7 +9775,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.08</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="15">
@@ -9036,7 +9785,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.22</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="16">
@@ -9046,7 +9795,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.93</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
@@ -9056,7 +9805,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>238.68</v>
+        <v>235.05</v>
       </c>
     </row>
     <row r="18">
@@ -9066,7 +9815,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.7</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="19">
@@ -9076,7 +9825,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.92</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="20">
@@ -9086,7 +9835,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.050000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -9096,7 +9845,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.64</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="22">
@@ -9106,7 +9855,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -9116,7 +9865,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -9126,7 +9875,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.53</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="25">
@@ -9146,7 +9895,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.33</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="27">
@@ -9156,7 +9905,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.52</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="28">
@@ -9166,7 +9915,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
